--- a/administrative_forms/030_payroll_processing_checklist_form--administrative_forms.xlsx
+++ b/administrative_forms/030_payroll_processing_checklist_form--administrative_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>pay_date</t>
+          <t>pay_date_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pay Date</t>
+          <t>Pay Date 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>pay_frequency</t>
+          <t>pay_frequency_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pay Frequency</t>
+          <t>Pay Frequency 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>tax_rate_value</t>
+          <t>tax_rate_value_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tax Rate</t>
+          <t>Tax Rate Value 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -825,9 +825,9 @@
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'employee_1',_'value':_'employee_1'}</t>
+          <t>employee_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Employee 1', 'value': 'employee_1'}</t>
+          <t>Employee 1</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'employee_2',_'value':_'employee_2'}</t>
+          <t>employee_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Employee 2', 'value': 'employee_2'}</t>
+          <t>Employee 2</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'tax_rate_1',_'value':_'tax_rate_1'}</t>
+          <t>tax_rate_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Tax Rate 1', 'value': 'tax_rate_1'}</t>
+          <t>Tax Rate 1</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'tax_rate_2',_'value':_'tax_rate_2'}</t>
+          <t>tax_rate_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Tax Rate 2', 'value': 'tax_rate_2'}</t>
+          <t>Tax Rate 2</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'daily',_'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Daily', 'value': 'daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'weekly',_'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly', 'value': 'weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -957,63 +957,63 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'monthly',_'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly', 'value': 'monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pay_frequency_choices</t>
+          <t>pay_frequency_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'daily',_'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Daily', 'value': 'daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pay_frequency_choices</t>
+          <t>pay_frequency_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'weekly',_'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly', 'value': 'weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pay_frequency_choices</t>
+          <t>pay_frequency_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'monthly',_'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly', 'value': 'monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'direct_deposit',_'value':_'direct_deposit'}</t>
+          <t>direct_deposit</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Direct Deposit', 'value': 'direct_deposit'}</t>
+          <t>Direct Deposit</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'check',_'value':_'check'}</t>
+          <t>check</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Check', 'value': 'check'}</t>
+          <t>Check</t>
         </is>
       </c>
     </row>
